--- a/decks/exceptional-grad/keyword-research.xlsx
+++ b/decks/exceptional-grad/keyword-research.xlsx
@@ -91,6 +91,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="009AA0A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007B3FE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="005B7A5E"/>
       </patternFill>
     </fill>
@@ -116,17 +126,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="009AA0A6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C2456B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007B3FE4"/>
       </patternFill>
     </fill>
   </fills>
@@ -920,17 +920,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Resume Review Service: What Expert Review Actually Changes</t>
+          <t>Is an Admissions Consultant Worth It? An Honest Answer</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>resume review service</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>Internship &amp; Career</t>
+          <t>is an admissions consultant worth it</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Essay &amp; Personal Statement Craft</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -943,20 +943,24 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>1300</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>Hard</t>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>/cover-letter-editing/</t>
+          <t>/college-personal-essay-editing/</t>
         </is>
       </c>
     </row>
@@ -976,17 +980,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Professional Resume Review: What Expert Review Actually Changes</t>
+          <t>Best Graduate School Admissions Consultants: An Honest Comparison</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>professional resume review</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>Internship &amp; Career</t>
+          <t>best graduate school admissions consultants</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Graduate School</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -999,20 +1003,24 @@
           <t>Commercial</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>260</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="K8" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>/cover-letter-editing/</t>
+          <t>/graduate-application-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -1032,38 +1040,38 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Personal Statement for Internship Example That Worked (With Analysis)</t>
+          <t>Resume Review Service: What Expert Review Actually Changes</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>personal statement for internship example</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
+          <t>resume review service</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Internship &amp; Career</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>140</v>
+        <v>1300</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>49</v>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1088,38 +1096,38 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Personal Statement Sample for Internship That Worked (With Analysis)</t>
+          <t>Professional Resume Review: What Expert Review Actually Changes</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>personal statement sample for internship</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
+          <t>professional resume review</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Internship &amp; Career</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>37</v>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1137,7 +1145,7 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
@@ -1152,7 +1160,7 @@
           <t>law school personal statement examples</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -1193,7 +1201,7 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
@@ -1208,7 +1216,7 @@
           <t>law school personal statement format</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -1249,7 +1257,7 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
@@ -1264,7 +1272,7 @@
           <t>law essay writing service</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -1285,7 +1293,7 @@
       <c r="J13" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -1312,15 +1320,15 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>What a Strong How Long Should a Law School Personal Statement Be Looks Like</t>
+          <t>Law School Diversity Statement Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>how long should a law school personal statement be</t>
-        </is>
-      </c>
-      <c r="F14" s="10" t="inlineStr">
+          <t>law school diversity statement examples</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -1336,14 +1344,14 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>590</v>
+        <v>480</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>5</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1361,22 +1369,22 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Law School Diversity Statement Examples That Worked (With Analysis)</t>
+          <t>Sample Law School Personal Statement That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>law school diversity statement examples</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
+          <t>sample law school personal statement</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -1392,19 +1400,19 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>480</v>
+        <v>390</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>20</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>/law-school-consulting-services/</t>
+          <t>/product/law-personal-essay-editing-unlimited/</t>
         </is>
       </c>
     </row>
@@ -1417,29 +1425,29 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sample Law School Personal Statement That Worked (With Analysis)</t>
+          <t>Law School Personal Statement Length, Explained for Applicants</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>sample law school personal statement</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
+          <t>law school personal statement length</t>
+        </is>
+      </c>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1451,7 +1459,7 @@
         <v>390</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
@@ -1473,41 +1481,41 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Understanding Law School Personal Statement Length</t>
+          <t>Law School Admissions Consulting: What to Expect</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>law school personal statement length</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
+          <t>law school admissions consulting</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial/Info</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
         <v>390</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
@@ -1516,7 +1524,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>/product/law-personal-essay-editing-unlimited/</t>
+          <t>/law-school-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -1529,45 +1537,45 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Law School Admissions Consulting: What to Expect</t>
+          <t>What a Strong How to Write a Law School Personal Statement Looks Like</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>law school admissions consulting</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
+          <t>how to write a law school personal statement</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Commercial/Info</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>14</v>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1585,29 +1593,29 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Writing a How to Write a Law School Personal Statement: A Practical Guide</t>
+          <t>How Many Words for Law School Personal Statement: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>how to write a law school personal statement</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
+          <t>how many words for law school personal statement</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1616,7 +1624,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>14</v>
@@ -1628,7 +1636,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>/law-school-consulting-services/</t>
+          <t>/product/law-personal-essay-editing-unlimited/</t>
         </is>
       </c>
     </row>
@@ -1641,22 +1649,22 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Law School Essay Examples That Worked (With Analysis)</t>
+          <t>Harvard Law School Personal Statement Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>law school essay examples</t>
-        </is>
-      </c>
-      <c r="F20" s="10" t="inlineStr">
+          <t>harvard law school personal statement examples</t>
+        </is>
+      </c>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -1672,19 +1680,19 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>9</v>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>/law-school-consulting-services/</t>
+          <t>/product/law-personal-essay-editing-unlimited/</t>
         </is>
       </c>
     </row>
@@ -1697,50 +1705,54 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>How Many Words for Law School Personal Statement: A Clear Guide for Applicants</t>
+          <t>Best Law School Admissions Consultants: An Honest Comparison</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>how many words for law school personal statement</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+          <t>best law school admissions consultants</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="J21" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>/product/law-personal-essay-editing-unlimited/</t>
+          <t>/law-school-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -1753,29 +1765,29 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Harvard Law School Personal Statement Examples That Worked (With Analysis)</t>
+          <t>MBA Admissions Consulting: How to Choose the Right One</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>harvard law school personal statement examples</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
-        <is>
-          <t>Law School</t>
+          <t>mba admissions consulting</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>MBA</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1784,19 +1796,19 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>110</v>
+        <v>720</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>47</v>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>/product/law-personal-essay-editing-unlimited/</t>
+          <t>/mba-application-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -1816,22 +1828,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MBA Admissions Consulting: How to Choose the Right One</t>
+          <t>MBA Essay Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>mba admissions consulting</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
+          <t>mba essay examples</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1840,14 +1852,14 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>720</v>
+        <v>320</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>11</v>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -1872,15 +1884,15 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MBA Essay Examples That Worked (With Analysis)</t>
+          <t>MBA Personal Statement Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>mba essay examples</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
+          <t>mba personal statement examples</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
@@ -1928,15 +1940,15 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MBA Personal Statement Examples That Worked (With Analysis)</t>
+          <t>MBA Statement of Purpose Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>mba personal statement examples</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr">
+          <t>mba statement of purpose examples</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
@@ -1952,10 +1964,10 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
@@ -1984,38 +1996,38 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MBA Personal Statement Format: Structure That Reads Well</t>
+          <t>Best MBA Admissions Consultants: An Honest Comparison</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>mba personal statement format</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
+          <t>best mba admissions consultants</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>320</v>
+        <v>170</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>30</v>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2040,34 +2052,34 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>MBA Statement of Purpose Examples That Worked (With Analysis)</t>
+          <t>Forte MBA Launch: A Complete Guide</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>mba statement of purpose examples</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
+          <t>forte mba launch</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>260</v>
+        <v>170</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -2096,34 +2108,34 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Forte MBA Launch: A Complete Guide</t>
+          <t>Statement of Purpose Sample for MBA That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>forte mba launch</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
+          <t>statement of purpose sample for mba</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
         <v>170</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -2145,29 +2157,29 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Statement of Purpose Sample for MBA That Worked (With Analysis)</t>
+          <t>MBA Essay Editing Service: What Expert Review Actually Changes</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>statement of purpose sample for mba</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
+          <t>mba essay editing service</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2176,19 +2188,21 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>90</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>/mba-application-consulting-services/</t>
+          <t>/mba-personal-essay-editing/</t>
         </is>
       </c>
     </row>
@@ -2201,29 +2215,29 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>MBA Essay Editing Service: What Expert Review Actually Changes</t>
+          <t>MBA Admission Essay Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>mba essay editing service</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
+          <t>mba admission essay examples</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2234,14 +2248,12 @@
       <c r="I30" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="J30" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2259,41 +2271,41 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>MBA Admission Essay Examples That Worked (With Analysis)</t>
+          <t>MBA Essay Services: What Expert Review Actually Changes</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>mba admission essay examples</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
+          <t>mba essay services</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial/Info</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -2315,34 +2327,34 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>MBA Essay Services: What Expert Review Actually Changes</t>
+          <t>Wharton MBA Essay Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>mba essay services</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
+          <t>wharton mba essay examples</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Commercial/Info</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -2358,7 +2370,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>/mba-personal-essay-editing/</t>
+          <t>/mba-application-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -2371,50 +2383,52 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Wharton MBA Essay Examples That Worked (With Analysis)</t>
+          <t>MBA Essay Review: What Expert Review Actually Changes</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>wharton mba essay examples</t>
-        </is>
-      </c>
-      <c r="F33" s="11" t="inlineStr">
+          <t>mba essay review</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>40</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>/mba-application-consulting-services/</t>
+          <t>/product/mba-personal-essay-editing-3-edits/</t>
         </is>
       </c>
     </row>
@@ -2427,52 +2441,50 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Refresh</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MBA Essay Review: What Expert Review Actually Changes</t>
+          <t>How Many Letters of Recommendation for Medical School: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>mba essay review</t>
+          <t>how many letters of recommendation for medical school</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>MBA</t>
+          <t>Medical &amp; Residency</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>BoFu</t>
+          <t>ToFu</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>2900</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="K34" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>/product/mba-personal-essay-editing-3-edits/</t>
+          <t>/who-should-you-ask-for-medical-school-letters-of-recommendation/</t>
         </is>
       </c>
     </row>
@@ -2485,22 +2497,22 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Medical School Personal Statement Examples That Worked (With Analysis)</t>
+          <t>Dental School Personal Statement Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>medical school personal statement examples</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
+          <t>dental school personal statement examples</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -2516,14 +2528,14 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>3600</v>
+        <v>1300</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>13</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2541,22 +2553,22 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>Refresh</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>How Many Letters of Recommendation for Medical School: A Clear Guide for Applicants</t>
+          <t>Residency Interview Questions: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>how many letters of recommendation for medical school</t>
-        </is>
-      </c>
-      <c r="F36" s="9" t="inlineStr">
+          <t>residency interview questions</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -2572,10 +2584,10 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2900</v>
+        <v>880</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
@@ -2584,7 +2596,7 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>/who-should-you-ask-for-medical-school-letters-of-recommendation/</t>
+          <t>/the-most-common-residency-interview-questions/</t>
         </is>
       </c>
     </row>
@@ -2597,22 +2609,22 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Dental School Personal Statement Examples That Worked (With Analysis)</t>
+          <t>Residency Personal Statement Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>dental school personal statement examples</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
+          <t>residency personal statement examples</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -2628,14 +2640,14 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1300</v>
+        <v>590</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>16</v>
+      </c>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2653,50 +2665,50 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>Refresh</t>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Residency Interview Questions: A Clear Guide for Applicants</t>
+          <t>Medical School Admissions Consulting: An Honest Look at Your Options</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>residency interview questions</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
+          <t>medical school admissions consulting</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>880</v>
+        <v>480</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>36</v>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>/the-most-common-residency-interview-questions/</t>
+          <t>/medical-school-personal-statement/</t>
         </is>
       </c>
     </row>
@@ -2709,45 +2721,45 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Residency Personal Statement Examples That Worked (With Analysis)</t>
+          <t>PA School Personal Statement: A Complete Guide</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>residency personal statement examples</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
+          <t>pa school personal statement</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>MoFu</t>
+          <t>BoFu</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>590</v>
+        <v>260</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="K39" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>2</v>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -2765,24 +2777,24 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>PA School Personal Statement: A Complete Guide</t>
+          <t>College Essay Review: What Expert Review Actually Changes</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>pa school personal statement</t>
-        </is>
-      </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Medical &amp; Residency</t>
+          <t>college essay review</t>
+        </is>
+      </c>
+      <c r="F40" s="14" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2792,23 +2804,23 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>260</v>
+        <v>2900</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>30</v>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>/medical-school-personal-statement/</t>
+          <t>/college-application-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -2828,15 +2840,15 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>College Essay Review: What Expert Review Actually Changes</t>
+          <t>Best College Admissions Consultants: An Honest Comparison</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>college essay review</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr">
+          <t>best college admissions consultants</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -2852,14 +2864,14 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>2900</v>
+        <v>720</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>68</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -2913,7 +2925,7 @@
       <c r="J42" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K42" s="8" t="inlineStr">
+      <c r="K42" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -2969,7 +2981,7 @@
       <c r="J43" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="K43" s="8" t="inlineStr">
+      <c r="K43" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3025,7 +3037,7 @@
       <c r="J44" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K44" s="8" t="inlineStr">
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3137,7 +3149,7 @@
       <c r="J46" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="K46" s="8" t="inlineStr">
+      <c r="K46" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3193,7 +3205,7 @@
       <c r="J47" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="K47" s="8" t="inlineStr">
+      <c r="K47" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3305,7 +3317,7 @@
       <c r="J49" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="K49" s="8" t="inlineStr">
+      <c r="K49" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3388,12 +3400,12 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>What a Strong How to Write an It Letter Looks Like</t>
+          <t>Research Statement Sample That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>how to write an it letter</t>
+          <t>research statement sample</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -3412,14 +3424,14 @@
         </is>
       </c>
       <c r="I51" s="2" t="n">
-        <v>1900</v>
+        <v>1000</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>22</v>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
@@ -3444,17 +3456,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Research Statement Sample That Worked (With Analysis)</t>
+          <t>Statement of Purpose Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>research statement sample</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>Essay &amp; Personal Statement Craft</t>
+          <t>statement of purpose examples</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>Graduate School</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -3468,19 +3480,19 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1000</v>
+        <v>4400</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K52" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>30</v>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>/college-personal-essay-editing/</t>
+          <t>/graduate-application-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -3500,15 +3512,15 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Statement of Purpose Examples That Worked (With Analysis)</t>
+          <t>Statement of Purpose Template: Structure That Reads Well</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>statement of purpose examples</t>
-        </is>
-      </c>
-      <c r="F53" s="14" t="inlineStr">
+          <t>statement of purpose template</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3527,9 +3539,9 @@
         <v>4400</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K53" s="8" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3556,15 +3568,15 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Statement of Purpose Template: Structure That Reads Well</t>
+          <t>Personal Statement Examples Graduate That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>statement of purpose template</t>
-        </is>
-      </c>
-      <c r="F54" s="14" t="inlineStr">
+          <t>personal statement examples graduate</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3580,12 +3592,12 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4400</v>
+        <v>2900</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K54" s="8" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3612,15 +3624,15 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Personal Statement Examples Graduate That Worked (With Analysis)</t>
+          <t>Letter of Intent Example That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>personal statement examples graduate</t>
-        </is>
-      </c>
-      <c r="F55" s="14" t="inlineStr">
+          <t>letter of intent example</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3639,9 +3651,9 @@
         <v>2900</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K55" s="8" t="inlineStr">
+        <v>41</v>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3668,15 +3680,15 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Letter of Intent Example That Worked (With Analysis)</t>
+          <t>SOP Letter Samples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>letter of intent example</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="inlineStr">
+          <t>sop letter samples</t>
+        </is>
+      </c>
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3692,14 +3704,14 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>22</v>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -3724,15 +3736,15 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Writing a How to Write a Personal Statement for Grad School: A Practical Guide</t>
+          <t>Personal Statement for Graduate School Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>how to write a personal statement for grad school</t>
-        </is>
-      </c>
-      <c r="F57" s="14" t="inlineStr">
+          <t>personal statement for graduate school examples</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3748,14 +3760,14 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>2900</v>
+        <v>2400</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>35</v>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -3780,15 +3792,15 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>SOP Letter Samples That Worked (With Analysis)</t>
+          <t>Statement of Purpose Grad School Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>sop letter samples</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="inlineStr">
+          <t>statement of purpose grad school examples</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3807,11 +3819,11 @@
         <v>2400</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="K58" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>41</v>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -3836,15 +3848,15 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Personal Statement for Graduate School Examples That Worked (With Analysis)</t>
+          <t>Sample Graduate Personal Statement That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>personal statement for graduate school examples</t>
-        </is>
-      </c>
-      <c r="F59" s="14" t="inlineStr">
+          <t>sample graduate personal statement</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3860,12 +3872,12 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>2400</v>
+        <v>1900</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K59" s="8" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3892,15 +3904,15 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Statement of Purpose Grad School Examples That Worked (With Analysis)</t>
+          <t>Graduate Statement of Purpose Example That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>statement of purpose grad school examples</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="inlineStr">
+          <t>graduate statement of purpose example</t>
+        </is>
+      </c>
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3912,16 +3924,16 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Transactional</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2400</v>
+        <v>1600</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="K60" s="8" t="inlineStr">
+        <v>35</v>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -3948,15 +3960,15 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Sample Graduate Personal Statement That Worked (With Analysis)</t>
+          <t>Academic SOP Sample That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>sample graduate personal statement</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="inlineStr">
+          <t>academic sop sample</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -3972,12 +3984,12 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K61" s="8" t="inlineStr">
+        <v>37</v>
+      </c>
+      <c r="K61" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4004,15 +4016,15 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Graduate Statement of Purpose Example That Worked (With Analysis)</t>
+          <t>Writing a Statement of Purpose Format: A Practical Guide</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>graduate statement of purpose example</t>
-        </is>
-      </c>
-      <c r="F62" s="14" t="inlineStr">
+          <t>statement of purpose format</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -4024,16 +4036,16 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Transactional</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="I62" s="2" t="n">
         <v>1600</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K62" s="8" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4060,15 +4072,15 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Academic SOP Sample That Worked (With Analysis)</t>
+          <t>What a Strong How to Write a Letter of Intent Looks Like</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>academic sop sample</t>
-        </is>
-      </c>
-      <c r="F63" s="14" t="inlineStr">
+          <t>how to write a letter of intent</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -4087,9 +4099,9 @@
         <v>1600</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="K63" s="8" t="inlineStr">
+        <v>41</v>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4116,15 +4128,15 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>What a Strong Statement of Purpose Format Looks Like</t>
+          <t>Graduate Statement of Intent Sample That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>statement of purpose format</t>
-        </is>
-      </c>
-      <c r="F64" s="14" t="inlineStr">
+          <t>graduate statement of intent sample</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -4143,9 +4155,9 @@
         <v>1600</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K64" s="8" t="inlineStr">
+        <v>42</v>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4172,15 +4184,15 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Writing a How to Write a Letter of Intent: A Practical Guide</t>
+          <t>How Long Should a Personal Statement Be for Grad School: The Exact Limits That Matter</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>how to write a letter of intent</t>
-        </is>
-      </c>
-      <c r="F65" s="14" t="inlineStr">
+          <t>how long should a personal statement be for grad school</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -4196,12 +4208,12 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="K65" s="8" t="inlineStr">
+        <v>33</v>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4228,15 +4240,15 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Graduate Statement of Intent Sample That Worked (With Analysis)</t>
+          <t>Statement of Purpose Format Example That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>graduate statement of intent sample</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="inlineStr">
+          <t>statement of purpose format example</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -4252,12 +4264,12 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="K66" s="8" t="inlineStr">
+        <v>36</v>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4284,17 +4296,17 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>How Long Should a Personal Statement Be for Grad School: The Exact Limits That Matter</t>
+          <t>Sample Cover Letter for It Internship That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>how long should a personal statement be for grad school</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="inlineStr">
-        <is>
-          <t>Graduate School</t>
+          <t>sample cover letter for it internship</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Internship &amp; Career</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -4308,19 +4320,19 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>1300</v>
+        <v>2400</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K67" s="8" t="inlineStr">
+        <v>42</v>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>/graduate-application-consulting-services/</t>
+          <t>/cover-letter-editing/</t>
         </is>
       </c>
     </row>
@@ -4340,17 +4352,17 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Statement of Purpose Format Example That Worked (With Analysis)</t>
+          <t>Example for Cover Letter for Internship That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>statement of purpose format example</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="inlineStr">
-        <is>
-          <t>Graduate School</t>
+          <t>example for cover letter for internship</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Internship &amp; Career</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -4369,14 +4381,14 @@
       <c r="J68" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="K68" s="8" t="inlineStr">
+      <c r="K68" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>/graduate-application-consulting-services/</t>
+          <t>/cover-letter-editing/</t>
         </is>
       </c>
     </row>
@@ -4396,15 +4408,15 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Sample Cover Letter for It Internship That Worked (With Analysis)</t>
+          <t>Personal Statement for Internship Example That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>sample cover letter for it internship</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr">
+          <t>personal statement for internship example</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
         <is>
           <t>Internship &amp; Career</t>
         </is>
@@ -4420,14 +4432,14 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>2400</v>
+        <v>140</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="K69" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>20</v>
+      </c>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
@@ -4452,15 +4464,15 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>What a Strong How to Write a Cover Letter for an Internship Looks Like</t>
+          <t>Personal Statement Sample for Internship That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>how to write a cover letter for an internship</t>
-        </is>
-      </c>
-      <c r="F70" s="7" t="inlineStr">
+          <t>personal statement sample for internship</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
         <is>
           <t>Internship &amp; Career</t>
         </is>
@@ -4476,14 +4488,14 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>2400</v>
+        <v>90</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="K70" s="4" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>14</v>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
@@ -4508,17 +4520,17 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Example for Cover Letter for Internship That Worked (With Analysis)</t>
+          <t>Writing a How Long Should a Law School Personal Statement Be: A Practical Guide</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>example for cover letter for internship</t>
-        </is>
-      </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>Internship &amp; Career</t>
+          <t>how long should a law school personal statement be</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
+          <t>Law School</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -4532,19 +4544,19 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1300</v>
+        <v>590</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="K71" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>16</v>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>/cover-letter-editing/</t>
+          <t>/law-school-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -4557,24 +4569,24 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>How Long Is Medical School: The Exact Limits That Matter</t>
+          <t>MBA Personal Statement Format: Structure That Reads Well</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>how long is medical school</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>Medical &amp; Residency</t>
+          <t>mba personal statement format</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="inlineStr">
+        <is>
+          <t>MBA</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -4588,19 +4600,19 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>9900</v>
+        <v>320</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="K72" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>20</v>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>/medical-school-personal-statement/</t>
+          <t>/mba-application-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -4613,22 +4625,22 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>How Long Does Medical School Take: The Exact Limits That Matter</t>
+          <t>How Long Is Medical School: The Exact Limits That Matter</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>how long does medical school take</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="inlineStr">
+          <t>how long is medical school</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -4644,14 +4656,14 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>2400</v>
+        <v>9900</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="K73" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>40</v>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -4669,24 +4681,24 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>College Essay Examples That Worked (With Analysis)</t>
+          <t>Medical School Personal Statement Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>college essay examples</t>
-        </is>
-      </c>
-      <c r="F74" s="13" t="inlineStr">
-        <is>
-          <t>Undergraduate</t>
+          <t>medical school personal statement examples</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr">
+        <is>
+          <t>Medical &amp; Residency</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
@@ -4700,19 +4712,19 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18100</v>
+        <v>3600</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="K74" s="4" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>20</v>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>/college-application-consulting-services/</t>
+          <t>/medical-school-personal-statement/</t>
         </is>
       </c>
     </row>
@@ -4732,17 +4744,17 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Common App Essay Examples That Worked (With Analysis)</t>
+          <t>How Long Does Medical School Take: The Exact Limits That Matter</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>common app essay examples</t>
-        </is>
-      </c>
-      <c r="F75" s="13" t="inlineStr">
-        <is>
-          <t>Undergraduate</t>
+          <t>how long does medical school take</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr">
+        <is>
+          <t>Medical &amp; Residency</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -4756,19 +4768,19 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>6600</v>
+        <v>2400</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="K75" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>26</v>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>/college-application-consulting-services/</t>
+          <t>/medical-school-personal-statement/</t>
         </is>
       </c>
     </row>
@@ -4788,15 +4800,15 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>College Essay Format: Structure That Reads Well</t>
+          <t>College Essay Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>college essay format</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="inlineStr">
+          <t>college essay examples</t>
+        </is>
+      </c>
+      <c r="F76" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -4812,10 +4824,10 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>5400</v>
+        <v>18100</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
@@ -4844,15 +4856,15 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Sample College Essays That Worked (With Analysis)</t>
+          <t>Common App Essay Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>sample college essays</t>
-        </is>
-      </c>
-      <c r="F77" s="13" t="inlineStr">
+          <t>common app essay examples</t>
+        </is>
+      </c>
+      <c r="F77" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -4868,12 +4880,12 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>3600</v>
+        <v>6600</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="K77" s="8" t="inlineStr">
+        <v>33</v>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -4893,22 +4905,22 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>Supporting</t>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Net-new</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>College Application Essay Examples That Worked (With Analysis)</t>
+          <t>Sample College Essays That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>college application essay examples</t>
-        </is>
-      </c>
-      <c r="F78" s="13" t="inlineStr">
+          <t>sample college essays</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -4927,16 +4939,16 @@
         <v>3600</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="K78" s="4" t="inlineStr">
-        <is>
-          <t>Hard</t>
+        <v>38</v>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>/college-personal-essay-editing/</t>
+          <t>/college-application-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -4949,22 +4961,22 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>Net-new</t>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>Supporting</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Good Common App Essay Examples That Worked (With Analysis)</t>
+          <t>College Application Essay Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>good common app essay examples</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="inlineStr">
+          <t>college application essay examples</t>
+        </is>
+      </c>
+      <c r="F79" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -4980,19 +4992,19 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>2900</v>
+        <v>3600</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>29</v>
-      </c>
-      <c r="K79" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>46</v>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>/college-application-consulting-services/</t>
+          <t>/college-personal-essay-editing/</t>
         </is>
       </c>
     </row>
@@ -5012,15 +5024,15 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>College Personal Statement Examples That Worked (With Analysis)</t>
+          <t>Good Common App Essay Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>college personal statement examples</t>
-        </is>
-      </c>
-      <c r="F80" s="13" t="inlineStr">
+          <t>good common app essay examples</t>
+        </is>
+      </c>
+      <c r="F80" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -5039,11 +5051,11 @@
         <v>2900</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="K80" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>29</v>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -5068,15 +5080,15 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Good College Essay Examples That Worked (With Analysis)</t>
+          <t>College Personal Statement Examples That Worked (With Analysis)</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>good college essay examples</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="inlineStr">
+          <t>college personal statement examples</t>
+        </is>
+      </c>
+      <c r="F81" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -5092,12 +5104,12 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="K81" s="8" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5321,7 +5333,7 @@
       <c r="J85" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="K85" s="8" t="inlineStr">
+      <c r="K85" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5377,7 +5389,7 @@
       <c r="J86" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="K86" s="8" t="inlineStr">
+      <c r="K86" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5489,7 +5501,7 @@
       <c r="J88" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="K88" s="8" t="inlineStr">
+      <c r="K88" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5804,7 +5816,7 @@
           <t>statement of purpose</t>
         </is>
       </c>
-      <c r="F94" s="14" t="inlineStr">
+      <c r="F94" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -5860,7 +5872,7 @@
           <t>personal statement for graduate school</t>
         </is>
       </c>
-      <c r="F95" s="14" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -5881,7 +5893,7 @@
       <c r="J95" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="K95" s="8" t="inlineStr">
+      <c r="K95" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -5908,22 +5920,22 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Graduate Studies Personal Statement: A Clear Guide for Applicants</t>
+          <t>What a Strong How to Write a Personal Statement for Grad School Looks Like</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>graduate studies personal statement</t>
-        </is>
-      </c>
-      <c r="F96" s="14" t="inlineStr">
+          <t>how to write a personal statement for grad school</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5932,14 +5944,14 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K96" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>49</v>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -5964,15 +5976,15 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Statement of Purpose vs Personal Statement, Explained for Applicants</t>
+          <t>Graduate Studies Personal Statement: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>statement of purpose vs personal statement</t>
-        </is>
-      </c>
-      <c r="F97" s="14" t="inlineStr">
+          <t>graduate studies personal statement</t>
+        </is>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>Graduate School</t>
         </is>
@@ -5984,18 +5996,18 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Commercial/Info</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="I97" s="2" t="n">
-        <v>720</v>
+        <v>2400</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K97" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>32</v>
+      </c>
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L97" s="2" t="inlineStr">
@@ -6020,22 +6032,22 @@
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Internship Application Letter: A Clear Guide for Applicants</t>
+          <t>Writing a How to Write a Cover Letter for an Internship: A Practical Guide</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>internship application letter</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
+          <t>how to write a cover letter for an internship</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
         <is>
           <t>Internship &amp; Career</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -6044,14 +6056,14 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1300</v>
+        <v>2400</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="K98" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>50</v>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -6076,17 +6088,17 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Law School Personal Statement: A Clear Guide for Applicants</t>
+          <t>Internship Application Letter: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>law school personal statement</t>
-        </is>
-      </c>
-      <c r="F99" s="10" t="inlineStr">
-        <is>
-          <t>Law School</t>
+          <t>internship application letter</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Internship &amp; Career</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -6100,19 +6112,19 @@
         </is>
       </c>
       <c r="I99" s="2" t="n">
-        <v>5400</v>
+        <v>1300</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="K99" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>32</v>
+      </c>
+      <c r="K99" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>/law-school-consulting-services/</t>
+          <t>/cover-letter-editing/</t>
         </is>
       </c>
     </row>
@@ -6132,15 +6144,15 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Law School Requirements: A Clear Guide for Applicants</t>
+          <t>Law School Personal Statement: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>law school requirements</t>
-        </is>
-      </c>
-      <c r="F100" s="10" t="inlineStr">
+          <t>law school personal statement</t>
+        </is>
+      </c>
+      <c r="F100" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -6156,14 +6168,14 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>4400</v>
+        <v>5400</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="K100" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>24</v>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>Easy</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -6188,15 +6200,15 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Law School Prerequisites, Explained for Applicants</t>
+          <t>Law School Requirements: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>law school prerequisites</t>
-        </is>
-      </c>
-      <c r="F101" s="10" t="inlineStr">
+          <t>law school requirements</t>
+        </is>
+      </c>
+      <c r="F101" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -6212,12 +6224,12 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>1900</v>
+        <v>4400</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="K101" s="8" t="inlineStr">
+        <v>34</v>
+      </c>
+      <c r="K101" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6244,15 +6256,15 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Diversity Statement Law School: A Clear Guide for Applicants</t>
+          <t>Understanding Law School Prerequisites</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>diversity statement law school</t>
-        </is>
-      </c>
-      <c r="F102" s="10" t="inlineStr">
+          <t>law school prerequisites</t>
+        </is>
+      </c>
+      <c r="F102" s="12" t="inlineStr">
         <is>
           <t>Law School</t>
         </is>
@@ -6268,14 +6280,14 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>720</v>
+        <v>1900</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>30</v>
+      </c>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -6300,17 +6312,17 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>MBA Scholarships: A Clear Guide for Applicants</t>
+          <t>Diversity Statement Law School: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>mba scholarships</t>
-        </is>
-      </c>
-      <c r="F103" s="11" t="inlineStr">
-        <is>
-          <t>MBA</t>
+          <t>diversity statement law school</t>
+        </is>
+      </c>
+      <c r="F103" s="12" t="inlineStr">
+        <is>
+          <t>Law School</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -6324,19 +6336,19 @@
         </is>
       </c>
       <c r="I103" s="2" t="n">
-        <v>2900</v>
+        <v>720</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="K103" s="8" t="inlineStr">
-        <is>
-          <t>Moderate</t>
+        <v>8</v>
+      </c>
+      <c r="K103" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>/mba-application-consulting-services/</t>
+          <t>/law-school-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -6356,15 +6368,15 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>What Does MBA Mean: A Clear Guide for Applicants</t>
+          <t>MBA Scholarships: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>what does mba mean</t>
-        </is>
-      </c>
-      <c r="F104" s="11" t="inlineStr">
+          <t>mba scholarships</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
@@ -6380,12 +6392,12 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>1000</v>
+        <v>2900</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>43</v>
-      </c>
-      <c r="K104" s="8" t="inlineStr">
+        <v>39</v>
+      </c>
+      <c r="K104" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6412,15 +6424,15 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Statement of Purpose for MBA, Explained for Applicants</t>
+          <t>What Does MBA Mean: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>statement of purpose for mba</t>
-        </is>
-      </c>
-      <c r="F105" s="11" t="inlineStr">
+          <t>what does mba mean</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
@@ -6436,14 +6448,14 @@
         </is>
       </c>
       <c r="I105" s="2" t="n">
-        <v>390</v>
+        <v>1000</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="K105" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>43</v>
+      </c>
+      <c r="K105" s="10" t="inlineStr">
+        <is>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -6476,7 +6488,7 @@
           <t>wharton sample essays</t>
         </is>
       </c>
-      <c r="F106" s="11" t="inlineStr">
+      <c r="F106" s="13" t="inlineStr">
         <is>
           <t>MBA</t>
         </is>
@@ -6499,7 +6511,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K106" s="12" t="inlineStr">
+      <c r="K106" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6534,7 +6546,7 @@
           <t>medical school acceptance rates</t>
         </is>
       </c>
-      <c r="F107" s="9" t="inlineStr">
+      <c r="F107" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6575,7 +6587,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="C108" s="10" t="inlineStr">
+      <c r="C108" s="12" t="inlineStr">
         <is>
           <t>Refresh</t>
         </is>
@@ -6590,7 +6602,7 @@
           <t>med school interview questions</t>
         </is>
       </c>
-      <c r="F108" s="9" t="inlineStr">
+      <c r="F108" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6611,7 +6623,7 @@
       <c r="J108" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="K108" s="8" t="inlineStr">
+      <c r="K108" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6646,7 +6658,7 @@
           <t>what is the mcat</t>
         </is>
       </c>
-      <c r="F109" s="9" t="inlineStr">
+      <c r="F109" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6687,7 +6699,7 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="C110" s="11" t="inlineStr">
         <is>
           <t>Supporting</t>
         </is>
@@ -6702,7 +6714,7 @@
           <t>medical school personal statement</t>
         </is>
       </c>
-      <c r="F110" s="9" t="inlineStr">
+      <c r="F110" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6750,7 +6762,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Understanding How to Get Into Medical School</t>
+          <t>How to Get Into Medical School, Explained for Applicants</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6758,7 +6770,7 @@
           <t>how to get into medical school</t>
         </is>
       </c>
-      <c r="F111" s="9" t="inlineStr">
+      <c r="F111" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6779,7 +6791,7 @@
       <c r="J111" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="K111" s="8" t="inlineStr">
+      <c r="K111" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6814,7 +6826,7 @@
           <t>how many years is medical school</t>
         </is>
       </c>
-      <c r="F112" s="9" t="inlineStr">
+      <c r="F112" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6835,7 +6847,7 @@
       <c r="J112" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="K112" s="8" t="inlineStr">
+      <c r="K112" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -6870,7 +6882,7 @@
           <t>letter of intent medical school</t>
         </is>
       </c>
-      <c r="F113" s="9" t="inlineStr">
+      <c r="F113" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6918,15 +6930,15 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>How Hard Is It to Get Into Medical School: A Clear Guide for Applicants</t>
+          <t>Average GPA for Medical School: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>how hard is it to get into medical school</t>
-        </is>
-      </c>
-      <c r="F114" s="9" t="inlineStr">
+          <t>average gpa for medical school</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6942,14 +6954,14 @@
         </is>
       </c>
       <c r="I114" s="2" t="n">
-        <v>1900</v>
+        <v>1300</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K114" s="6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+        <v>14</v>
+      </c>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>Very Easy</t>
         </is>
       </c>
       <c r="L114" s="2" t="inlineStr">
@@ -6974,15 +6986,15 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Average GPA for Medical School: A Clear Guide for Applicants</t>
+          <t>Update Letter Medical School: A Clear Guide for Applicants</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>average gpa for medical school</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="inlineStr">
+          <t>update letter medical school</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr">
         <is>
           <t>Medical &amp; Residency</t>
         </is>
@@ -6998,10 +7010,10 @@
         </is>
       </c>
       <c r="I115" s="2" t="n">
-        <v>1300</v>
+        <v>1000</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
@@ -7030,22 +7042,22 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Update Letter Medical School: A Clear Guide for Applicants</t>
+          <t>College Essay Format: Structure That Reads Well</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>update letter medical school</t>
-        </is>
-      </c>
-      <c r="F116" s="9" t="inlineStr">
-        <is>
-          <t>Medical &amp; Residency</t>
+          <t>college essay format</t>
+        </is>
+      </c>
+      <c r="F116" s="14" t="inlineStr">
+        <is>
+          <t>Undergraduate</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>ToFu</t>
+          <t>MoFu</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -7054,19 +7066,19 @@
         </is>
       </c>
       <c r="I116" s="2" t="n">
-        <v>1000</v>
+        <v>5400</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="K116" s="5" t="inlineStr">
-        <is>
-          <t>Very Easy</t>
+        <v>50</v>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>Hard</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>/medical-school-personal-statement/</t>
+          <t>/college-application-consulting-services/</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7106,7 @@
           <t>how to start a college essay</t>
         </is>
       </c>
-      <c r="F117" s="13" t="inlineStr">
+      <c r="F117" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -7115,7 +7127,7 @@
       <c r="J117" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="K117" s="8" t="inlineStr">
+      <c r="K117" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7150,7 +7162,7 @@
           <t>college essay ideas</t>
         </is>
       </c>
-      <c r="F118" s="13" t="inlineStr">
+      <c r="F118" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -7171,7 +7183,7 @@
       <c r="J118" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="K118" s="8" t="inlineStr">
+      <c r="K118" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7206,7 +7218,7 @@
           <t>college essay hooks</t>
         </is>
       </c>
-      <c r="F119" s="13" t="inlineStr">
+      <c r="F119" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -7262,7 +7274,7 @@
           <t>what is a personal statement for college</t>
         </is>
       </c>
-      <c r="F120" s="13" t="inlineStr">
+      <c r="F120" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -7318,7 +7330,7 @@
           <t>good hooks for college essays</t>
         </is>
       </c>
-      <c r="F121" s="13" t="inlineStr">
+      <c r="F121" s="14" t="inlineStr">
         <is>
           <t>Undergraduate</t>
         </is>
@@ -7500,7 +7512,7 @@
       <c r="C5" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7528,7 +7540,7 @@
       <c r="C6" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7668,7 +7680,7 @@
       <c r="C11" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7808,7 +7820,7 @@
       <c r="C16" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -7892,7 +7904,7 @@
       <c r="C19" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8060,7 +8072,7 @@
       <c r="C25" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8088,7 +8100,7 @@
       <c r="C26" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D26" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8116,7 +8128,7 @@
       <c r="C27" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D27" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8172,7 +8184,7 @@
       <c r="C29" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D29" s="8" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8228,7 +8240,7 @@
       <c r="C31" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8340,7 +8352,7 @@
       <c r="C35" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8368,7 +8380,7 @@
       <c r="C36" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8396,7 +8408,7 @@
       <c r="C37" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8424,7 +8436,7 @@
       <c r="C38" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8536,7 +8548,7 @@
       <c r="C42" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D42" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8564,7 +8576,7 @@
       <c r="C43" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8676,7 +8688,7 @@
       <c r="C47" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D47" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8760,7 +8772,7 @@
       <c r="C50" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8816,7 +8828,7 @@
       <c r="C52" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D52" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8872,7 +8884,7 @@
       <c r="C54" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D54" s="8" t="inlineStr">
+      <c r="D54" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8956,7 +8968,7 @@
       <c r="C57" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D57" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -8984,7 +8996,7 @@
       <c r="C58" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D58" s="8" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9012,7 +9024,7 @@
       <c r="C59" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D59" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9040,7 +9052,7 @@
       <c r="C60" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D60" s="8" t="inlineStr">
+      <c r="D60" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9096,7 +9108,7 @@
       <c r="C62" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D62" s="8" t="inlineStr">
+      <c r="D62" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9152,7 +9164,7 @@
       <c r="C64" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D64" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9180,7 +9192,7 @@
       <c r="C65" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D65" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9208,7 +9220,7 @@
       <c r="C66" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D66" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9348,7 +9360,7 @@
       <c r="C71" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D71" s="8" t="inlineStr">
+      <c r="D71" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9460,7 +9472,7 @@
       <c r="C75" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D75" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9470,9 +9482,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9528,7 @@
       <c r="C77" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D77" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9656,7 +9668,7 @@
       <c r="C82" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D82" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9684,7 +9696,7 @@
       <c r="C83" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D83" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9712,7 +9724,7 @@
       <c r="C84" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9768,7 +9780,7 @@
       <c r="C86" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D86" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9796,7 +9808,7 @@
       <c r="C87" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D87" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9824,7 +9836,7 @@
       <c r="C88" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D88" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9880,7 +9892,7 @@
       <c r="C90" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D90" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -9936,7 +9948,7 @@
       <c r="C92" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="D92" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10020,7 +10032,7 @@
       <c r="C95" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D95" s="8" t="inlineStr">
+      <c r="D95" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10048,7 +10060,7 @@
       <c r="C96" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D96" s="8" t="inlineStr">
+      <c r="D96" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10160,7 +10172,7 @@
       <c r="C100" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D100" s="8" t="inlineStr">
+      <c r="D100" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10188,7 +10200,7 @@
       <c r="C101" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D101" s="8" t="inlineStr">
+      <c r="D101" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10216,7 +10228,7 @@
       <c r="C102" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D102" s="8" t="inlineStr">
+      <c r="D102" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10310,9 +10322,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10506,9 +10518,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -10524,7 +10536,7 @@
       <c r="C113" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D113" s="8" t="inlineStr">
+      <c r="D113" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10664,7 +10676,7 @@
       <c r="C118" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D118" s="8" t="inlineStr">
+      <c r="D118" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10748,7 +10760,7 @@
       <c r="C121" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D121" s="8" t="inlineStr">
+      <c r="D121" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10804,7 +10816,7 @@
       <c r="C123" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D123" s="8" t="inlineStr">
+      <c r="D123" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10832,7 +10844,7 @@
       <c r="C124" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D124" s="8" t="inlineStr">
+      <c r="D124" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10888,7 +10900,7 @@
       <c r="C126" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D126" s="8" t="inlineStr">
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10944,7 +10956,7 @@
       <c r="C128" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D128" s="8" t="inlineStr">
+      <c r="D128" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -10972,7 +10984,7 @@
       <c r="C129" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D129" s="8" t="inlineStr">
+      <c r="D129" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11000,7 +11012,7 @@
       <c r="C130" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D130" s="8" t="inlineStr">
+      <c r="D130" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11028,7 +11040,7 @@
       <c r="C131" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D131" s="8" t="inlineStr">
+      <c r="D131" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11056,7 +11068,7 @@
       <c r="C132" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D132" s="8" t="inlineStr">
+      <c r="D132" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11084,7 +11096,7 @@
       <c r="C133" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D133" s="8" t="inlineStr">
+      <c r="D133" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11112,7 +11124,7 @@
       <c r="C134" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D134" s="8" t="inlineStr">
+      <c r="D134" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11140,7 +11152,7 @@
       <c r="C135" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D135" s="8" t="inlineStr">
+      <c r="D135" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11196,7 +11208,7 @@
       <c r="C137" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D137" s="8" t="inlineStr">
+      <c r="D137" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11224,7 +11236,7 @@
       <c r="C138" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D138" s="8" t="inlineStr">
+      <c r="D138" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11308,7 +11320,7 @@
       <c r="C141" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D141" s="8" t="inlineStr">
+      <c r="D141" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11476,7 +11488,7 @@
       <c r="C147" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D147" s="8" t="inlineStr">
+      <c r="D147" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11560,7 +11572,7 @@
       <c r="C150" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D150" s="8" t="inlineStr">
+      <c r="D150" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11588,7 +11600,7 @@
       <c r="C151" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D151" s="8" t="inlineStr">
+      <c r="D151" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11616,7 +11628,7 @@
       <c r="C152" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D152" s="8" t="inlineStr">
+      <c r="D152" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11644,7 +11656,7 @@
       <c r="C153" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D153" s="8" t="inlineStr">
+      <c r="D153" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11672,7 +11684,7 @@
       <c r="C154" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D154" s="8" t="inlineStr">
+      <c r="D154" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11700,7 +11712,7 @@
       <c r="C155" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D155" s="8" t="inlineStr">
+      <c r="D155" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11728,7 +11740,7 @@
       <c r="C156" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D156" s="8" t="inlineStr">
+      <c r="D156" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11784,7 +11796,7 @@
       <c r="C158" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D158" s="8" t="inlineStr">
+      <c r="D158" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11812,7 +11824,7 @@
       <c r="C159" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D159" s="8" t="inlineStr">
+      <c r="D159" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11868,7 +11880,7 @@
       <c r="C161" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D161" s="8" t="inlineStr">
+      <c r="D161" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11952,7 +11964,7 @@
       <c r="C164" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D164" s="8" t="inlineStr">
+      <c r="D164" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -11980,7 +11992,7 @@
       <c r="C165" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D165" s="8" t="inlineStr">
+      <c r="D165" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12008,7 +12020,7 @@
       <c r="C166" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D166" s="8" t="inlineStr">
+      <c r="D166" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12064,7 +12076,7 @@
       <c r="C168" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D168" s="8" t="inlineStr">
+      <c r="D168" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12092,7 +12104,7 @@
       <c r="C169" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D169" s="8" t="inlineStr">
+      <c r="D169" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12232,7 +12244,7 @@
       <c r="C174" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D174" s="8" t="inlineStr">
+      <c r="D174" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12260,7 +12272,7 @@
       <c r="C175" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D175" s="8" t="inlineStr">
+      <c r="D175" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12288,7 +12300,7 @@
       <c r="C176" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D176" s="8" t="inlineStr">
+      <c r="D176" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12316,7 +12328,7 @@
       <c r="C177" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D177" s="8" t="inlineStr">
+      <c r="D177" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12344,7 +12356,7 @@
       <c r="C178" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D178" s="8" t="inlineStr">
+      <c r="D178" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12372,7 +12384,7 @@
       <c r="C179" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D179" s="8" t="inlineStr">
+      <c r="D179" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12400,7 +12412,7 @@
       <c r="C180" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D180" s="8" t="inlineStr">
+      <c r="D180" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12652,7 +12664,7 @@
       <c r="C189" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D189" s="8" t="inlineStr">
+      <c r="D189" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12680,7 +12692,7 @@
       <c r="C190" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D190" s="8" t="inlineStr">
+      <c r="D190" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12820,7 +12832,7 @@
       <c r="C195" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D195" s="8" t="inlineStr">
+      <c r="D195" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12848,7 +12860,7 @@
       <c r="C196" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D196" s="8" t="inlineStr">
+      <c r="D196" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -12876,7 +12888,7 @@
       <c r="C197" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D197" s="8" t="inlineStr">
+      <c r="D197" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13044,7 +13056,7 @@
       <c r="C203" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D203" s="8" t="inlineStr">
+      <c r="D203" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13072,7 +13084,7 @@
       <c r="C204" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D204" s="8" t="inlineStr">
+      <c r="D204" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13100,7 +13112,7 @@
       <c r="C205" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D205" s="8" t="inlineStr">
+      <c r="D205" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13128,7 +13140,7 @@
       <c r="C206" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D206" s="8" t="inlineStr">
+      <c r="D206" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13296,7 +13308,7 @@
       <c r="C212" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D212" s="8" t="inlineStr">
+      <c r="D212" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13324,7 +13336,7 @@
       <c r="C213" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D213" s="8" t="inlineStr">
+      <c r="D213" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13352,7 +13364,7 @@
       <c r="C214" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D214" s="8" t="inlineStr">
+      <c r="D214" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13464,7 +13476,7 @@
       <c r="C218" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D218" s="8" t="inlineStr">
+      <c r="D218" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13492,7 +13504,7 @@
       <c r="C219" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D219" s="8" t="inlineStr">
+      <c r="D219" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13548,7 +13560,7 @@
       <c r="C221" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D221" s="8" t="inlineStr">
+      <c r="D221" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13772,7 +13784,7 @@
       <c r="C229" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D229" s="8" t="inlineStr">
+      <c r="D229" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13828,7 +13840,7 @@
       <c r="C231" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D231" s="8" t="inlineStr">
+      <c r="D231" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -13856,7 +13868,7 @@
       <c r="C232" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D232" s="8" t="inlineStr">
+      <c r="D232" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14024,7 +14036,7 @@
       <c r="C238" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D238" s="8" t="inlineStr">
+      <c r="D238" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14080,7 +14092,7 @@
       <c r="C240" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D240" s="8" t="inlineStr">
+      <c r="D240" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14192,7 +14204,7 @@
       <c r="C244" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D244" s="8" t="inlineStr">
+      <c r="D244" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14248,7 +14260,7 @@
       <c r="C246" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D246" s="8" t="inlineStr">
+      <c r="D246" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14276,7 +14288,7 @@
       <c r="C247" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D247" s="8" t="inlineStr">
+      <c r="D247" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14332,7 +14344,7 @@
       <c r="C249" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D249" s="8" t="inlineStr">
+      <c r="D249" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14416,7 +14428,7 @@
       <c r="C252" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D252" s="8" t="inlineStr">
+      <c r="D252" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14444,7 +14456,7 @@
       <c r="C253" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D253" s="8" t="inlineStr">
+      <c r="D253" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14472,7 +14484,7 @@
       <c r="C254" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D254" s="8" t="inlineStr">
+      <c r="D254" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14500,7 +14512,7 @@
       <c r="C255" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D255" s="8" t="inlineStr">
+      <c r="D255" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14528,7 +14540,7 @@
       <c r="C256" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D256" s="8" t="inlineStr">
+      <c r="D256" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14584,7 +14596,7 @@
       <c r="C258" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D258" s="8" t="inlineStr">
+      <c r="D258" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14668,7 +14680,7 @@
       <c r="C261" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D261" s="8" t="inlineStr">
+      <c r="D261" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14696,7 +14708,7 @@
       <c r="C262" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D262" s="8" t="inlineStr">
+      <c r="D262" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14780,7 +14792,7 @@
       <c r="C265" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D265" s="8" t="inlineStr">
+      <c r="D265" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -14920,7 +14932,7 @@
       <c r="C270" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D270" s="8" t="inlineStr">
+      <c r="D270" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15032,7 +15044,7 @@
       <c r="C274" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D274" s="8" t="inlineStr">
+      <c r="D274" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15060,7 +15072,7 @@
       <c r="C275" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D275" s="8" t="inlineStr">
+      <c r="D275" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15098,9 +15110,9 @@
           <t>Commercial/Info</t>
         </is>
       </c>
-      <c r="F276" s="3" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -15284,7 +15296,7 @@
       <c r="C283" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D283" s="8" t="inlineStr">
+      <c r="D283" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15424,7 +15436,7 @@
       <c r="C288" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D288" s="8" t="inlineStr">
+      <c r="D288" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15592,7 +15604,7 @@
       <c r="C294" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D294" s="8" t="inlineStr">
+      <c r="D294" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15648,7 +15660,7 @@
       <c r="C296" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D296" s="8" t="inlineStr">
+      <c r="D296" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15816,7 +15828,7 @@
       <c r="C302" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D302" s="8" t="inlineStr">
+      <c r="D302" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15844,7 +15856,7 @@
       <c r="C303" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D303" s="8" t="inlineStr">
+      <c r="D303" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15872,7 +15884,7 @@
       <c r="C304" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D304" s="8" t="inlineStr">
+      <c r="D304" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -15928,7 +15940,7 @@
       <c r="C306" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D306" s="8" t="inlineStr">
+      <c r="D306" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16040,7 +16052,7 @@
       <c r="C310" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D310" s="8" t="inlineStr">
+      <c r="D310" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16096,7 +16108,7 @@
       <c r="C312" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D312" s="8" t="inlineStr">
+      <c r="D312" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16460,7 +16472,7 @@
       <c r="C325" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D325" s="8" t="inlineStr">
+      <c r="D325" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16488,7 +16500,7 @@
       <c r="C326" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D326" s="8" t="inlineStr">
+      <c r="D326" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16516,7 +16528,7 @@
       <c r="C327" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D327" s="8" t="inlineStr">
+      <c r="D327" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16628,7 +16640,7 @@
       <c r="C331" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D331" s="8" t="inlineStr">
+      <c r="D331" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16656,7 +16668,7 @@
       <c r="C332" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D332" s="8" t="inlineStr">
+      <c r="D332" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16684,7 +16696,7 @@
       <c r="C333" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D333" s="8" t="inlineStr">
+      <c r="D333" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16796,7 +16808,7 @@
       <c r="C337" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D337" s="8" t="inlineStr">
+      <c r="D337" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16880,7 +16892,7 @@
       <c r="C340" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D340" s="8" t="inlineStr">
+      <c r="D340" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16936,7 +16948,7 @@
       <c r="C342" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D342" s="8" t="inlineStr">
+      <c r="D342" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -16964,7 +16976,7 @@
       <c r="C343" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D343" s="8" t="inlineStr">
+      <c r="D343" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17020,7 +17032,7 @@
       <c r="C345" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D345" s="8" t="inlineStr">
+      <c r="D345" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17048,7 +17060,7 @@
       <c r="C346" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D346" s="8" t="inlineStr">
+      <c r="D346" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17076,7 +17088,7 @@
       <c r="C347" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D347" s="8" t="inlineStr">
+      <c r="D347" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17104,7 +17116,7 @@
       <c r="C348" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D348" s="8" t="inlineStr">
+      <c r="D348" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17188,7 +17200,7 @@
       <c r="C351" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D351" s="8" t="inlineStr">
+      <c r="D351" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17216,7 +17228,7 @@
       <c r="C352" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D352" s="8" t="inlineStr">
+      <c r="D352" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17244,7 +17256,7 @@
       <c r="C353" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D353" s="8" t="inlineStr">
+      <c r="D353" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17272,7 +17284,7 @@
       <c r="C354" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D354" s="8" t="inlineStr">
+      <c r="D354" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17328,7 +17340,7 @@
       <c r="C356" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D356" s="8" t="inlineStr">
+      <c r="D356" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17384,7 +17396,7 @@
       <c r="C358" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D358" s="8" t="inlineStr">
+      <c r="D358" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17524,7 +17536,7 @@
       <c r="C363" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D363" s="8" t="inlineStr">
+      <c r="D363" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17552,7 +17564,7 @@
       <c r="C364" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D364" s="8" t="inlineStr">
+      <c r="D364" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17664,7 +17676,7 @@
       <c r="C368" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D368" s="8" t="inlineStr">
+      <c r="D368" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17748,7 +17760,7 @@
       <c r="C371" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D371" s="8" t="inlineStr">
+      <c r="D371" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17860,7 +17872,7 @@
       <c r="C375" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D375" s="8" t="inlineStr">
+      <c r="D375" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -17888,7 +17900,7 @@
       <c r="C376" s="2" t="n">
         <v>39</v>
       </c>
-      <c r="D376" s="8" t="inlineStr">
+      <c r="D376" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18028,7 +18040,7 @@
       <c r="C381" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D381" s="8" t="inlineStr">
+      <c r="D381" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18168,7 +18180,7 @@
       <c r="C386" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D386" s="8" t="inlineStr">
+      <c r="D386" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18178,9 +18190,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F386" s="2" t="inlineStr">
-        <is>
-          <t>Overflow</t>
+      <c r="F386" s="3" t="inlineStr">
+        <is>
+          <t>Yes (planned)</t>
         </is>
       </c>
     </row>
@@ -18224,7 +18236,7 @@
       <c r="C388" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D388" s="8" t="inlineStr">
+      <c r="D388" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18364,7 +18376,7 @@
       <c r="C393" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D393" s="8" t="inlineStr">
+      <c r="D393" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18392,7 +18404,7 @@
       <c r="C394" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D394" s="8" t="inlineStr">
+      <c r="D394" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18448,7 +18460,7 @@
       <c r="C396" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D396" s="8" t="inlineStr">
+      <c r="D396" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18476,7 +18488,7 @@
       <c r="C397" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D397" s="8" t="inlineStr">
+      <c r="D397" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18616,7 +18628,7 @@
       <c r="C402" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D402" s="8" t="inlineStr">
+      <c r="D402" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18672,7 +18684,7 @@
       <c r="C404" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D404" s="8" t="inlineStr">
+      <c r="D404" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18728,7 +18740,7 @@
       <c r="C406" s="2" t="n">
         <v>40</v>
       </c>
-      <c r="D406" s="8" t="inlineStr">
+      <c r="D406" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18784,7 +18796,7 @@
       <c r="C408" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D408" s="8" t="inlineStr">
+      <c r="D408" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18812,7 +18824,7 @@
       <c r="C409" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D409" s="8" t="inlineStr">
+      <c r="D409" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18840,7 +18852,7 @@
       <c r="C410" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D410" s="8" t="inlineStr">
+      <c r="D410" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18868,7 +18880,7 @@
       <c r="C411" s="2" t="n">
         <v>41</v>
       </c>
-      <c r="D411" s="8" t="inlineStr">
+      <c r="D411" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -18924,7 +18936,7 @@
       <c r="C413" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="D413" s="8" t="inlineStr">
+      <c r="D413" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19120,7 +19132,7 @@
       <c r="C420" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="D420" s="8" t="inlineStr">
+      <c r="D420" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19232,7 +19244,7 @@
       <c r="C424" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D424" s="8" t="inlineStr">
+      <c r="D424" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19260,7 +19272,7 @@
       <c r="C425" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D425" s="8" t="inlineStr">
+      <c r="D425" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19288,7 +19300,7 @@
       <c r="C426" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D426" s="8" t="inlineStr">
+      <c r="D426" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19372,7 +19384,7 @@
       <c r="C429" s="2" t="n">
         <v>37</v>
       </c>
-      <c r="D429" s="8" t="inlineStr">
+      <c r="D429" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19484,7 +19496,7 @@
       <c r="C433" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="D433" s="8" t="inlineStr">
+      <c r="D433" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19512,7 +19524,7 @@
       <c r="C434" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="D434" s="8" t="inlineStr">
+      <c r="D434" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19568,7 +19580,7 @@
       <c r="C436" s="2" t="n">
         <v>43</v>
       </c>
-      <c r="D436" s="8" t="inlineStr">
+      <c r="D436" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19596,7 +19608,7 @@
       <c r="C437" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="D437" s="8" t="inlineStr">
+      <c r="D437" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19690,9 +19702,9 @@
           <t>Informational</t>
         </is>
       </c>
-      <c r="F440" s="3" t="inlineStr">
-        <is>
-          <t>Yes (planned)</t>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>Overflow</t>
         </is>
       </c>
     </row>
@@ -19764,7 +19776,7 @@
       <c r="C443" s="2" t="n">
         <v>32</v>
       </c>
-      <c r="D443" s="8" t="inlineStr">
+      <c r="D443" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19820,7 +19832,7 @@
       <c r="C445" s="2" t="n">
         <v>42</v>
       </c>
-      <c r="D445" s="8" t="inlineStr">
+      <c r="D445" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -19904,7 +19916,7 @@
       <c r="C448" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="D448" s="8" t="inlineStr">
+      <c r="D448" s="10" t="inlineStr">
         <is>
           <t>Moderate</t>
         </is>
@@ -23580,7 +23592,7 @@
         <is>
           <t>KD is SEMrush's 0-100 ranking-difficulty score. We front-load winnable terms for a young domain:
   Very Easy (&lt;15) · Easy (15-29) · Moderate (30-44) · Hard (45+).
-55 of the 120 articles target KD under 30 — realistic wins while your domain authority builds. Your law and medical verticals are the most winnable (difficulty in the teens).</t>
+51 of the 120 articles target KD under 30 — realistic wins while your domain authority builds. Your law and medical verticals are the most winnable (difficulty in the teens).</t>
         </is>
       </c>
     </row>
@@ -23613,9 +23625,9 @@
     <row r="17" ht="65" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>BoFu (14) — consultant / editing-service intent for applicants ready to hire.
-MoFu (63) — 'how do I write this essay' and 'examples that worked' guidance, searched once someone has decided to apply. This is where your insider read is decisive, and it's the bulk of the plan.
-ToFu (43) — requirements and process education that builds topical authority and earns AI citations.
+          <t>BoFu (20) — consultant / editing-service intent for applicants ready to hire.
+MoFu (60) — 'how do I write this essay' and 'examples that worked' guidance, searched once someone has decided to apply. This is where your insider read is decisive, and it's the bulk of the plan.
+ToFu (40) — requirements and process education that builds topical authority and earns AI citations.
 The MoFu weighting is deliberate: those terms are winnable at a young domain and are exactly what applicants search when they're closest to buying.</t>
         </is>
       </c>
